--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/45.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/45.xlsx
@@ -426,13 +426,13 @@
         <v>-14.55862286463122</v>
       </c>
       <c r="E2">
-        <v>-17.14283512480444</v>
+        <v>-15.61724846848914</v>
       </c>
       <c r="F2">
-        <v>1.794681853572302</v>
+        <v>1.569859626982905</v>
       </c>
       <c r="G2">
-        <v>-12.9304352195712</v>
+        <v>-12.73998923388326</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-13.81607757502949</v>
       </c>
       <c r="E3">
-        <v>-17.42818981529943</v>
+        <v>-16.55963703736068</v>
       </c>
       <c r="F3">
-        <v>1.469464811233216</v>
+        <v>1.76751471623009</v>
       </c>
       <c r="G3">
-        <v>-13.33468943892066</v>
+        <v>-12.93223010647759</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-12.96174980291901</v>
       </c>
       <c r="E4">
-        <v>-17.21716099467357</v>
+        <v>-16.70522370714123</v>
       </c>
       <c r="F4">
-        <v>2.104424992827093</v>
+        <v>1.616572921561575</v>
       </c>
       <c r="G4">
-        <v>-12.71213519984068</v>
+        <v>-12.50832611796312</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-12.07574633173495</v>
       </c>
       <c r="E5">
-        <v>-19.52556153433784</v>
+        <v>-17.1629532804619</v>
       </c>
       <c r="F5">
-        <v>1.564735346229188</v>
+        <v>1.541494670376245</v>
       </c>
       <c r="G5">
-        <v>-12.66592763132256</v>
+        <v>-12.26135490113299</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-11.15656217503654</v>
       </c>
       <c r="E6">
-        <v>-19.22711176853566</v>
+        <v>-18.54964409044096</v>
       </c>
       <c r="F6">
-        <v>1.548916842305328</v>
+        <v>2.047678512265716</v>
       </c>
       <c r="G6">
-        <v>-11.94950407046909</v>
+        <v>-12.40076605155384</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-10.23772141040988</v>
       </c>
       <c r="E7">
-        <v>-20.55440750335834</v>
+        <v>-18.31532821391678</v>
       </c>
       <c r="F7">
-        <v>1.703175420054652</v>
+        <v>1.802349222252615</v>
       </c>
       <c r="G7">
-        <v>-11.79316615749175</v>
+        <v>-12.01326498024556</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-9.311392773472658</v>
       </c>
       <c r="E8">
-        <v>-20.98608398203837</v>
+        <v>-18.86236429035525</v>
       </c>
       <c r="F8">
-        <v>1.696578302058757</v>
+        <v>2.011709142901356</v>
       </c>
       <c r="G8">
-        <v>-11.86754496552028</v>
+        <v>-11.49355319209871</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-8.398249112937645</v>
       </c>
       <c r="E9">
-        <v>-21.2845420542632</v>
+        <v>-19.57674986391635</v>
       </c>
       <c r="F9">
-        <v>1.985925379121819</v>
+        <v>1.921536380902213</v>
       </c>
       <c r="G9">
-        <v>-10.55361464919396</v>
+        <v>-10.8186221950318</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-7.49130270247932</v>
       </c>
       <c r="E10">
-        <v>-21.96199311951261</v>
+        <v>-20.40861317301156</v>
       </c>
       <c r="F10">
-        <v>1.887636273310046</v>
+        <v>2.051641421920709</v>
       </c>
       <c r="G10">
-        <v>-10.01711838407084</v>
+        <v>-10.65863576648838</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-6.597149344128193</v>
       </c>
       <c r="E11">
-        <v>-21.04126770091137</v>
+        <v>-21.50599958852571</v>
       </c>
       <c r="F11">
-        <v>2.470392741179498</v>
+        <v>2.215694615840734</v>
       </c>
       <c r="G11">
-        <v>-10.06553855862993</v>
+        <v>-9.670885352514286</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-5.724223706389222</v>
       </c>
       <c r="E12">
-        <v>-22.14374595350975</v>
+        <v>-21.86212915320711</v>
       </c>
       <c r="F12">
-        <v>2.638055960240924</v>
+        <v>2.383883019835535</v>
       </c>
       <c r="G12">
-        <v>-9.616916040326792</v>
+        <v>-9.368234785789479</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-4.869164220911683</v>
       </c>
       <c r="E13">
-        <v>-23.56143633281733</v>
+        <v>-23.40273382167298</v>
       </c>
       <c r="F13">
-        <v>2.571485042282344</v>
+        <v>2.167430617484024</v>
       </c>
       <c r="G13">
-        <v>-8.836529236991051</v>
+        <v>-8.705161790655414</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-4.051893350822682</v>
       </c>
       <c r="E14">
-        <v>-23.68136030982175</v>
+        <v>-23.75895891021485</v>
       </c>
       <c r="F14">
-        <v>2.763356470323183</v>
+        <v>2.656086205130258</v>
       </c>
       <c r="G14">
-        <v>-8.234528084704603</v>
+        <v>-8.037966429811979</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-3.270094845672658</v>
       </c>
       <c r="E15">
-        <v>-25.14910519201616</v>
+        <v>-24.73739735338591</v>
       </c>
       <c r="F15">
-        <v>2.013977212850221</v>
+        <v>2.715715404253377</v>
       </c>
       <c r="G15">
-        <v>-7.696068539648966</v>
+        <v>-7.967221778254287</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-2.531503402469766</v>
       </c>
       <c r="E16">
-        <v>-24.81595119238371</v>
+        <v>-25.43201779425215</v>
       </c>
       <c r="F16">
-        <v>2.731010379978668</v>
+        <v>2.705359154983578</v>
       </c>
       <c r="G16">
-        <v>-7.540094825542084</v>
+        <v>-7.022916765020907</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-1.837910997199844</v>
       </c>
       <c r="E17">
-        <v>-27.17660328372566</v>
+        <v>-26.42613045696312</v>
       </c>
       <c r="F17">
-        <v>2.581213389060822</v>
+        <v>2.894132488937946</v>
       </c>
       <c r="G17">
-        <v>-6.672108403568424</v>
+        <v>-6.476649788265545</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-1.186627182142321</v>
       </c>
       <c r="E18">
-        <v>-28.08925278290577</v>
+        <v>-26.65033326391133</v>
       </c>
       <c r="F18">
-        <v>2.771505948831924</v>
+        <v>3.038331372947673</v>
       </c>
       <c r="G18">
-        <v>-6.088301530337445</v>
+        <v>-5.872868108167959</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-0.5877908156736937</v>
       </c>
       <c r="E19">
-        <v>-29.05726251244018</v>
+        <v>-27.25951799461453</v>
       </c>
       <c r="F19">
-        <v>3.13352072793817</v>
+        <v>3.116839065180593</v>
       </c>
       <c r="G19">
-        <v>-5.307931696841545</v>
+        <v>-5.728527871959078</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-0.04273150066514641</v>
       </c>
       <c r="E20">
-        <v>-28.74539164424182</v>
+        <v>-28.78717917998658</v>
       </c>
       <c r="F20">
-        <v>3.022151700836193</v>
+        <v>3.372509693850244</v>
       </c>
       <c r="G20">
-        <v>-5.624150303206369</v>
+        <v>-4.888740102314032</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>0.4327719163323441</v>
       </c>
       <c r="E21">
-        <v>-29.41561612178602</v>
+        <v>-28.91764608393908</v>
       </c>
       <c r="F21">
-        <v>2.974126272291489</v>
+        <v>3.174003042912982</v>
       </c>
       <c r="G21">
-        <v>-4.488155284487383</v>
+        <v>-4.85025250555184</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>0.8288452551191745</v>
       </c>
       <c r="E22">
-        <v>-29.57125148636699</v>
+        <v>-29.82049192778693</v>
       </c>
       <c r="F22">
-        <v>3.437341040262945</v>
+        <v>3.521801380652382</v>
       </c>
       <c r="G22">
-        <v>-4.353934294313658</v>
+        <v>-4.583165501647177</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>1.130819277381818</v>
       </c>
       <c r="E23">
-        <v>-28.61362270853898</v>
+        <v>-29.77792151170744</v>
       </c>
       <c r="F23">
-        <v>4.039850757219553</v>
+        <v>3.472132471180524</v>
       </c>
       <c r="G23">
-        <v>-4.534013013230288</v>
+        <v>-3.985618279633168</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>1.325069756747446</v>
       </c>
       <c r="E24">
-        <v>-31.29914937273733</v>
+        <v>-30.59896155209015</v>
       </c>
       <c r="F24">
-        <v>3.059860641746432</v>
+        <v>3.725559880923393</v>
       </c>
       <c r="G24">
-        <v>-3.63315731685451</v>
+        <v>-3.513175327680717</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>1.406280479002181</v>
       </c>
       <c r="E25">
-        <v>-31.94183390598659</v>
+        <v>-30.92110331189481</v>
       </c>
       <c r="F25">
-        <v>3.2200205088733</v>
+        <v>3.44627581106954</v>
       </c>
       <c r="G25">
-        <v>-3.555847948022464</v>
+        <v>-3.784207166662552</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>1.368552467625403</v>
       </c>
       <c r="E26">
-        <v>-32.3349748133892</v>
+        <v>-30.38991796647755</v>
       </c>
       <c r="F26">
-        <v>3.167674315955593</v>
+        <v>3.682252833105035</v>
       </c>
       <c r="G26">
-        <v>-4.574805897466432</v>
+        <v>-3.503620002477243</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>1.220325606789527</v>
       </c>
       <c r="E27">
-        <v>-32.18416340376203</v>
+        <v>-30.98826696883427</v>
       </c>
       <c r="F27">
-        <v>3.344497621757176</v>
+        <v>3.178693259147632</v>
       </c>
       <c r="G27">
-        <v>-4.964960790651584</v>
+        <v>-3.735018127821387</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>0.9696165783360999</v>
       </c>
       <c r="E28">
-        <v>-31.55795673644402</v>
+        <v>-30.78642505165893</v>
       </c>
       <c r="F28">
-        <v>3.510890125222707</v>
+        <v>3.353467183994689</v>
       </c>
       <c r="G28">
-        <v>-3.564452962194773</v>
+        <v>-3.535136911181162</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>0.6325389550779613</v>
       </c>
       <c r="E29">
-        <v>-31.55907187368473</v>
+        <v>-30.85962332465337</v>
       </c>
       <c r="F29">
-        <v>3.407562888867108</v>
+        <v>3.499321146075209</v>
       </c>
       <c r="G29">
-        <v>-4.034742049859556</v>
+        <v>-3.569739719991778</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>0.2225663331969647</v>
       </c>
       <c r="E30">
-        <v>-32.20002659441721</v>
+        <v>-30.70021892079513</v>
       </c>
       <c r="F30">
-        <v>3.520643323023268</v>
+        <v>3.32029438298218</v>
       </c>
       <c r="G30">
-        <v>-4.304815745576452</v>
+        <v>-3.762611087404863</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-0.2416219248441993</v>
       </c>
       <c r="E31">
-        <v>-30.94529161465061</v>
+        <v>-30.40874862662432</v>
       </c>
       <c r="F31">
-        <v>2.693117541505007</v>
+        <v>3.420281641969691</v>
       </c>
       <c r="G31">
-        <v>-4.394359063562455</v>
+        <v>-3.925409287872914</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-0.7378360521883608</v>
       </c>
       <c r="E32">
-        <v>-30.13382472637164</v>
+        <v>-30.19511574249779</v>
       </c>
       <c r="F32">
-        <v>3.337807726612167</v>
+        <v>3.877116324204785</v>
       </c>
       <c r="G32">
-        <v>-4.556118187683244</v>
+        <v>-3.732263792277762</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-1.245995093870051</v>
       </c>
       <c r="E33">
-        <v>-31.1760211931958</v>
+        <v>-29.87150997570113</v>
       </c>
       <c r="F33">
-        <v>3.482858172311972</v>
+        <v>3.567719442524364</v>
       </c>
       <c r="G33">
-        <v>-4.374256330210883</v>
+        <v>-4.087648788998467</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-1.742968086956093</v>
       </c>
       <c r="E34">
-        <v>-30.55909279997745</v>
+        <v>-29.86519501788172</v>
       </c>
       <c r="F34">
-        <v>3.754549426551764</v>
+        <v>3.40350388859339</v>
       </c>
       <c r="G34">
-        <v>-4.800306350779252</v>
+        <v>-4.215280259824222</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-2.214736546621848</v>
       </c>
       <c r="E35">
-        <v>-29.98178811940364</v>
+        <v>-29.43936626074705</v>
       </c>
       <c r="F35">
-        <v>3.840277169067485</v>
+        <v>3.577411341137118</v>
       </c>
       <c r="G35">
-        <v>-3.740639060926053</v>
+        <v>-4.706643277828471</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-2.645750155630841</v>
       </c>
       <c r="E36">
-        <v>-29.6041573796936</v>
+        <v>-28.367654997643</v>
       </c>
       <c r="F36">
-        <v>4.150760868780379</v>
+        <v>3.599275270366609</v>
       </c>
       <c r="G36">
-        <v>-4.725075134641731</v>
+        <v>-4.307995632488428</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-3.029116710642687</v>
       </c>
       <c r="E37">
-        <v>-29.21157507921419</v>
+        <v>-28.44972453002727</v>
       </c>
       <c r="F37">
-        <v>3.394378593284151</v>
+        <v>3.749779687046445</v>
       </c>
       <c r="G37">
-        <v>-4.517071891578554</v>
+        <v>-5.00629670976268</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-3.359729991005659</v>
       </c>
       <c r="E38">
-        <v>-28.51562768732965</v>
+        <v>-28.06482151728746</v>
       </c>
       <c r="F38">
-        <v>3.138427976432354</v>
+        <v>3.779423642923028</v>
       </c>
       <c r="G38">
-        <v>-4.365322362220094</v>
+        <v>-5.101369584792662</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-3.633513237619723</v>
       </c>
       <c r="E39">
-        <v>-28.02536600970159</v>
+        <v>-26.83522592567005</v>
       </c>
       <c r="F39">
-        <v>3.873416835383883</v>
+        <v>3.77609526269858</v>
       </c>
       <c r="G39">
-        <v>-5.326494090884361</v>
+        <v>-5.0792957392748</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-3.854485175136771</v>
       </c>
       <c r="E40">
-        <v>-26.33152445619485</v>
+        <v>-26.80438417837187</v>
       </c>
       <c r="F40">
-        <v>3.520088316863393</v>
+        <v>4.030200276976939</v>
       </c>
       <c r="G40">
-        <v>-6.054523716817621</v>
+        <v>-5.373876494468476</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-4.024073190887163</v>
       </c>
       <c r="E41">
-        <v>-27.18089770423553</v>
+        <v>-26.66494010814075</v>
       </c>
       <c r="F41">
-        <v>4.0837459458939</v>
+        <v>4.110888232214028</v>
       </c>
       <c r="G41">
-        <v>-5.458921499523991</v>
+        <v>-5.504831443158718</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-4.154035480986754</v>
       </c>
       <c r="E42">
-        <v>-26.41816875085342</v>
+        <v>-25.81815015754411</v>
       </c>
       <c r="F42">
-        <v>4.016759187499114</v>
+        <v>3.9299976424647</v>
       </c>
       <c r="G42">
-        <v>-4.697568329629761</v>
+        <v>-5.581310595210791</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-4.255965139365844</v>
       </c>
       <c r="E43">
-        <v>-27.28875244913</v>
+        <v>-24.77843523448654</v>
       </c>
       <c r="F43">
-        <v>4.137737276473565</v>
+        <v>4.39311631981743</v>
       </c>
       <c r="G43">
-        <v>-5.045306455443096</v>
+        <v>-6.026139701623037</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-4.339815879208579</v>
       </c>
       <c r="E44">
-        <v>-26.42400816597613</v>
+        <v>-24.80129866282972</v>
       </c>
       <c r="F44">
-        <v>3.911682439188803</v>
+        <v>4.472041509221362</v>
       </c>
       <c r="G44">
-        <v>-5.56683923794225</v>
+        <v>-6.016902887259678</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-4.419160178308818</v>
       </c>
       <c r="E45">
-        <v>-25.11940557783231</v>
+        <v>-23.90002688607397</v>
       </c>
       <c r="F45">
-        <v>4.361409729107877</v>
+        <v>4.34774332369649</v>
       </c>
       <c r="G45">
-        <v>-6.661814237645665</v>
+        <v>-6.331625536973793</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-4.495807707561528</v>
       </c>
       <c r="E46">
-        <v>-23.30820673191988</v>
+        <v>-23.42227052774497</v>
       </c>
       <c r="F46">
-        <v>4.237784177914079</v>
+        <v>4.475654847832374</v>
       </c>
       <c r="G46">
-        <v>-5.999050615745645</v>
+        <v>-6.299659580200203</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-4.578805122325024</v>
       </c>
       <c r="E47">
-        <v>-24.79133510886145</v>
+        <v>-23.18711570253318</v>
       </c>
       <c r="F47">
-        <v>3.734733221541995</v>
+        <v>4.843070582404872</v>
       </c>
       <c r="G47">
-        <v>-5.350364128680909</v>
+        <v>-6.421714500579339</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-4.669889054433071</v>
       </c>
       <c r="E48">
-        <v>-23.01352392878932</v>
+        <v>-22.96111040186999</v>
       </c>
       <c r="F48">
-        <v>4.03598228144848</v>
+        <v>4.625779872241728</v>
       </c>
       <c r="G48">
-        <v>-6.9764429005545</v>
+        <v>-6.829136858490115</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-4.768495184379261</v>
       </c>
       <c r="E49">
-        <v>-21.80300818999817</v>
+        <v>-21.92049838516625</v>
       </c>
       <c r="F49">
-        <v>4.534174034635742</v>
+        <v>4.540800973858138</v>
       </c>
       <c r="G49">
-        <v>-6.115957147791107</v>
+        <v>-6.391724877461222</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-4.879639644274096</v>
       </c>
       <c r="E50">
-        <v>-22.73237644136638</v>
+        <v>-21.40745219021018</v>
       </c>
       <c r="F50">
-        <v>4.007057348477526</v>
+        <v>4.600720101572238</v>
       </c>
       <c r="G50">
-        <v>-6.628172182844579</v>
+        <v>-6.859982805834118</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-4.997525951831221</v>
       </c>
       <c r="E51">
-        <v>-21.10593735445027</v>
+        <v>-21.18050411057624</v>
       </c>
       <c r="F51">
-        <v>5.052102469562104</v>
+        <v>4.793342030480012</v>
       </c>
       <c r="G51">
-        <v>-6.342969222222181</v>
+        <v>-6.938373022926886</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-5.12980438987044</v>
       </c>
       <c r="E52">
-        <v>-21.15172235609518</v>
+        <v>-20.24571176521781</v>
       </c>
       <c r="F52">
-        <v>4.128550681976519</v>
+        <v>4.626858406600173</v>
       </c>
       <c r="G52">
-        <v>-7.191894597936123</v>
+        <v>-7.254534192910705</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-5.27354412443819</v>
       </c>
       <c r="E53">
-        <v>-20.21143946536533</v>
+        <v>-19.67312097949767</v>
       </c>
       <c r="F53">
-        <v>4.252075172347176</v>
+        <v>4.872422952955669</v>
       </c>
       <c r="G53">
-        <v>-6.38360807252745</v>
+        <v>-7.110460252650118</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-5.43472244136109</v>
       </c>
       <c r="E54">
-        <v>-20.64581553140649</v>
+        <v>-18.89590147180323</v>
       </c>
       <c r="F54">
-        <v>4.339005704331761</v>
+        <v>4.471042498133586</v>
       </c>
       <c r="G54">
-        <v>-7.884807098374319</v>
+        <v>-7.318468717202478</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-5.621715669793747</v>
       </c>
       <c r="E55">
-        <v>-19.76747363437513</v>
+        <v>-19.01866209214252</v>
       </c>
       <c r="F55">
-        <v>4.277211152817724</v>
+        <v>4.696247430463076</v>
       </c>
       <c r="G55">
-        <v>-7.224267830865928</v>
+        <v>-7.614989255627352</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-5.835631086175263</v>
       </c>
       <c r="E56">
-        <v>-19.89634778178456</v>
+        <v>-17.80897699561633</v>
       </c>
       <c r="F56">
-        <v>4.169877931702186</v>
+        <v>4.577048674669839</v>
       </c>
       <c r="G56">
-        <v>-8.387436784661517</v>
+        <v>-8.03868307920224</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-6.092241345132383</v>
       </c>
       <c r="E57">
-        <v>-18.48043913013534</v>
+        <v>-16.80042361712895</v>
       </c>
       <c r="F57">
-        <v>4.141312510184048</v>
+        <v>4.615713551562909</v>
       </c>
       <c r="G57">
-        <v>-7.474319726313577</v>
+        <v>-7.959128470021836</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-6.388054031855494</v>
       </c>
       <c r="E58">
-        <v>-17.55807319306079</v>
+        <v>-16.86537568903794</v>
       </c>
       <c r="F58">
-        <v>4.094481587434181</v>
+        <v>4.76515434449755</v>
       </c>
       <c r="G58">
-        <v>-7.735391574680314</v>
+        <v>-8.049769606108402</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-6.73440998429612</v>
       </c>
       <c r="E59">
-        <v>-18.34470803082862</v>
+        <v>-16.92649019368279</v>
       </c>
       <c r="F59">
-        <v>3.493981489796763</v>
+        <v>4.643351201589911</v>
       </c>
       <c r="G59">
-        <v>-7.596781922848927</v>
+        <v>-7.903821151231397</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-7.129191255979194</v>
       </c>
       <c r="E60">
-        <v>-16.15977000421752</v>
+        <v>-16.0717800690897</v>
       </c>
       <c r="F60">
-        <v>4.422440525876533</v>
+        <v>4.574715992063555</v>
       </c>
       <c r="G60">
-        <v>-8.026802885940379</v>
+        <v>-8.640964886532233</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-7.565421179098753</v>
       </c>
       <c r="E61">
-        <v>-17.59259468559276</v>
+        <v>-15.37236266914327</v>
       </c>
       <c r="F61">
-        <v>4.119668926683703</v>
+        <v>4.415735720118274</v>
       </c>
       <c r="G61">
-        <v>-7.868303276441596</v>
+        <v>-8.105383687388297</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-8.042956712479636</v>
       </c>
       <c r="E62">
-        <v>-15.99718008727313</v>
+        <v>-14.90933775138344</v>
       </c>
       <c r="F62">
-        <v>4.051799128637533</v>
+        <v>4.36166817973755</v>
       </c>
       <c r="G62">
-        <v>-7.787930198831877</v>
+        <v>-8.57833181841913</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-8.540785690967141</v>
       </c>
       <c r="E63">
-        <v>-16.81870190016951</v>
+        <v>-14.44003317810046</v>
       </c>
       <c r="F63">
-        <v>4.395884723677587</v>
+        <v>4.030871254573207</v>
       </c>
       <c r="G63">
-        <v>-8.568127723184762</v>
+        <v>-8.808929750546097</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-9.055740486122916</v>
       </c>
       <c r="E64">
-        <v>-16.25614942622149</v>
+        <v>-15.23205057774527</v>
       </c>
       <c r="F64">
-        <v>3.973293093139419</v>
+        <v>4.355187033178047</v>
       </c>
       <c r="G64">
-        <v>-8.982181372356965</v>
+        <v>-8.523395225360629</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-9.565731429914958</v>
       </c>
       <c r="E65">
-        <v>-16.78244021209244</v>
+        <v>-13.27713400714847</v>
       </c>
       <c r="F65">
-        <v>4.851847963404936</v>
+        <v>3.96921586878284</v>
       </c>
       <c r="G65">
-        <v>-9.190773338325439</v>
+        <v>-9.12080929940049</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-10.05772571735745</v>
       </c>
       <c r="E66">
-        <v>-16.41798345870476</v>
+        <v>-13.99005765032324</v>
       </c>
       <c r="F66">
-        <v>3.521826231674466</v>
+        <v>3.755038163319417</v>
       </c>
       <c r="G66">
-        <v>-8.879516452056027</v>
+        <v>-8.577408920206171</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-10.52024393383181</v>
       </c>
       <c r="E67">
-        <v>-15.68236666885113</v>
+        <v>-13.60177392356502</v>
       </c>
       <c r="F67">
-        <v>4.616081346689751</v>
+        <v>3.855944910124035</v>
       </c>
       <c r="G67">
-        <v>-8.839608610236269</v>
+        <v>-8.891598978023699</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-10.93077762370243</v>
       </c>
       <c r="E68">
-        <v>-15.31210372603134</v>
+        <v>-13.73211415457211</v>
       </c>
       <c r="F68">
-        <v>3.642400077356351</v>
+        <v>3.594792145982658</v>
       </c>
       <c r="G68">
-        <v>-8.905608233499613</v>
+        <v>-8.655360532207631</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-11.28882582212474</v>
       </c>
       <c r="E69">
-        <v>-14.56303468469659</v>
+        <v>-13.2813536698545</v>
       </c>
       <c r="F69">
-        <v>3.904903080364292</v>
+        <v>3.872808813710228</v>
       </c>
       <c r="G69">
-        <v>-8.368773876951943</v>
+        <v>-8.469408943333292</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-11.57586839372268</v>
       </c>
       <c r="E70">
-        <v>-14.6258146270827</v>
+        <v>-14.06040059053186</v>
       </c>
       <c r="F70">
-        <v>3.244425869294579</v>
+        <v>3.786961786288504</v>
       </c>
       <c r="G70">
-        <v>-9.332809592432662</v>
+        <v>-8.777651724972264</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-11.79461214033345</v>
       </c>
       <c r="E71">
-        <v>-13.88499801665038</v>
+        <v>-13.51958187144666</v>
       </c>
       <c r="F71">
-        <v>3.554503668980101</v>
+        <v>3.550466206258856</v>
       </c>
       <c r="G71">
-        <v>-8.493848123450704</v>
+        <v>-8.591580041846735</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-11.94271399985381</v>
       </c>
       <c r="E72">
-        <v>-15.09657282432936</v>
+        <v>-13.69667895554868</v>
       </c>
       <c r="F72">
-        <v>3.458934921719122</v>
+        <v>3.450097898266057</v>
       </c>
       <c r="G72">
-        <v>-8.415905649055311</v>
+        <v>-8.730732728553072</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-12.01422080030981</v>
       </c>
       <c r="E73">
-        <v>-15.15641229309749</v>
+        <v>-13.94857952882218</v>
       </c>
       <c r="F73">
-        <v>3.24687618007206</v>
+        <v>3.58806414593712</v>
       </c>
       <c r="G73">
-        <v>-7.733933473826177</v>
+        <v>-8.564214217042684</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-12.02004952432533</v>
       </c>
       <c r="E74">
-        <v>-15.55894984112252</v>
+        <v>-13.93081209077456</v>
       </c>
       <c r="F74">
-        <v>3.495959631154649</v>
+        <v>3.405125831968072</v>
       </c>
       <c r="G74">
-        <v>-7.960718413477824</v>
+        <v>-8.214886147773361</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-11.95188788537962</v>
       </c>
       <c r="E75">
-        <v>-15.92569501395018</v>
+        <v>-13.93800129957784</v>
       </c>
       <c r="F75">
-        <v>3.300087188558289</v>
+        <v>3.331333206991886</v>
       </c>
       <c r="G75">
-        <v>-8.162347523621799</v>
+        <v>-8.016109276095179</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-11.82022435587794</v>
       </c>
       <c r="E76">
-        <v>-18.02961634724785</v>
+        <v>-14.21845935392086</v>
       </c>
       <c r="F76">
-        <v>2.676020038311225</v>
+        <v>3.405158966664183</v>
       </c>
       <c r="G76">
-        <v>-7.941922357794104</v>
+        <v>-8.004870020630436</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-11.62460248737745</v>
       </c>
       <c r="E77">
-        <v>-15.0998912401779</v>
+        <v>-13.71642332218691</v>
       </c>
       <c r="F77">
-        <v>3.025576171679366</v>
+        <v>3.292999677059936</v>
       </c>
       <c r="G77">
-        <v>-8.163839564155619</v>
+        <v>-7.86532311149084</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-11.36439486847971</v>
       </c>
       <c r="E78">
-        <v>-15.56022072378792</v>
+        <v>-14.09404990868562</v>
       </c>
       <c r="F78">
-        <v>3.076592006548176</v>
+        <v>3.170127940202685</v>
       </c>
       <c r="G78">
-        <v>-7.486289990263831</v>
+        <v>-7.942622037344522</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-11.0504589694713</v>
       </c>
       <c r="E79">
-        <v>-17.45242795659113</v>
+        <v>-15.01089207469815</v>
       </c>
       <c r="F79">
-        <v>2.81089481883504</v>
+        <v>3.25818836532469</v>
       </c>
       <c r="G79">
-        <v>-7.496234316411382</v>
+        <v>-7.309124862310884</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-10.67467873294755</v>
       </c>
       <c r="E80">
-        <v>-17.90990003080967</v>
+        <v>-16.08085898904578</v>
       </c>
       <c r="F80">
-        <v>2.687128445182767</v>
+        <v>2.982123331198115</v>
       </c>
       <c r="G80">
-        <v>-7.180201072912527</v>
+        <v>-6.888061363911541</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-10.24719436784208</v>
       </c>
       <c r="E81">
-        <v>-18.39810586883194</v>
+        <v>-16.12318851886843</v>
       </c>
       <c r="F81">
-        <v>2.676369609355207</v>
+        <v>3.059297351912528</v>
       </c>
       <c r="G81">
-        <v>-6.699873672294914</v>
+        <v>-6.713854209580325</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-9.763156329037658</v>
       </c>
       <c r="E82">
-        <v>-18.14193994752784</v>
+        <v>-17.05886965145038</v>
       </c>
       <c r="F82">
-        <v>2.883226203712688</v>
+        <v>2.856519638646432</v>
       </c>
       <c r="G82">
-        <v>-6.538670636772033</v>
+        <v>-6.594882578563293</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-9.225176460578499</v>
       </c>
       <c r="E83">
-        <v>-18.82604445731962</v>
+        <v>-17.76017260933827</v>
       </c>
       <c r="F83">
-        <v>2.573529453032454</v>
+        <v>2.764734873681441</v>
       </c>
       <c r="G83">
-        <v>-5.422794015872165</v>
+        <v>-6.24984396265717</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-8.641314769519868</v>
       </c>
       <c r="E84">
-        <v>-20.31865461571578</v>
+        <v>-18.2180101661534</v>
       </c>
       <c r="F84">
-        <v>2.692035693676951</v>
+        <v>2.840994376783164</v>
       </c>
       <c r="G84">
-        <v>-6.246034886298736</v>
+        <v>-6.101642435198033</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-8.008176014238874</v>
       </c>
       <c r="E85">
-        <v>-19.38066429763722</v>
+        <v>-20.23706477923952</v>
       </c>
       <c r="F85">
-        <v>2.539912647092044</v>
+        <v>2.738908034796958</v>
       </c>
       <c r="G85">
-        <v>-5.689834026374188</v>
+        <v>-5.298741875880826</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-7.345349639228216</v>
       </c>
       <c r="E86">
-        <v>-21.58852389755005</v>
+        <v>-20.41285360177421</v>
       </c>
       <c r="F86">
-        <v>2.14265083499668</v>
+        <v>2.754670209737427</v>
       </c>
       <c r="G86">
-        <v>-4.751271345868962</v>
+        <v>-4.996963297849451</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-6.6590240611256</v>
       </c>
       <c r="E87">
-        <v>-22.66842529338667</v>
+        <v>-21.6756998032582</v>
       </c>
       <c r="F87">
-        <v>2.914453998063423</v>
+        <v>2.778219038264211</v>
       </c>
       <c r="G87">
-        <v>-5.354473440667322</v>
+        <v>-4.966067746358216</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-5.970235147082604</v>
       </c>
       <c r="E88">
-        <v>-23.72189565235208</v>
+        <v>-22.69654253405576</v>
       </c>
       <c r="F88">
-        <v>2.371903170456248</v>
+        <v>2.463936445642079</v>
       </c>
       <c r="G88">
-        <v>-5.253126946384896</v>
+        <v>-5.046961667513862</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-5.29973152787237</v>
       </c>
       <c r="E89">
-        <v>-25.66801987457421</v>
+        <v>-24.13478715620991</v>
       </c>
       <c r="F89">
-        <v>2.617573747839303</v>
+        <v>2.397365527683499</v>
       </c>
       <c r="G89">
-        <v>-5.248064712622726</v>
+        <v>-4.719527302385615</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-4.661930153091867</v>
       </c>
       <c r="E90">
-        <v>-26.92180376894743</v>
+        <v>-25.24884040877059</v>
       </c>
       <c r="F90">
-        <v>2.454628909504224</v>
+        <v>2.200850271982567</v>
       </c>
       <c r="G90">
-        <v>-4.139492955088794</v>
+        <v>-4.598618498881977</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-4.085535827784103</v>
       </c>
       <c r="E91">
-        <v>-28.36287257480246</v>
+        <v>-26.90118722793098</v>
       </c>
       <c r="F91">
-        <v>2.066727649060494</v>
+        <v>2.144226389796804</v>
       </c>
       <c r="G91">
-        <v>-4.218937912996371</v>
+        <v>-4.715968857507928</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-3.578745070578532</v>
       </c>
       <c r="E92">
-        <v>-28.92775292369805</v>
+        <v>-28.3179742837754</v>
       </c>
       <c r="F92">
-        <v>2.239402490908856</v>
+        <v>2.12452118601901</v>
       </c>
       <c r="G92">
-        <v>-5.184610565335718</v>
+        <v>-3.998995734918033</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-3.158742080770817</v>
       </c>
       <c r="E93">
-        <v>-29.64263272940681</v>
+        <v>-30.48923163228251</v>
       </c>
       <c r="F93">
-        <v>2.177606282660013</v>
+        <v>2.018712160924623</v>
       </c>
       <c r="G93">
-        <v>-4.963096719013529</v>
+        <v>-4.124274924867195</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-2.826124408620326</v>
       </c>
       <c r="E94">
-        <v>-33.24236427042641</v>
+        <v>-31.96130208407173</v>
       </c>
       <c r="F94">
-        <v>1.893224439809332</v>
+        <v>1.627515654952556</v>
       </c>
       <c r="G94">
-        <v>-4.956225239249719</v>
+        <v>-3.844016714500366</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-2.576403098082832</v>
       </c>
       <c r="E95">
-        <v>-34.32973106361941</v>
+        <v>-34.36704559076733</v>
       </c>
       <c r="F95">
-        <v>1.706029974124699</v>
+        <v>1.35820844209802</v>
       </c>
       <c r="G95">
-        <v>-4.300662050931991</v>
+        <v>-4.323320703238263</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-2.403729343975274</v>
       </c>
       <c r="E96">
-        <v>-37.81856770905477</v>
+        <v>-36.31165596746157</v>
       </c>
       <c r="F96">
-        <v>0.9779430723732961</v>
+        <v>1.186655209713048</v>
       </c>
       <c r="G96">
-        <v>-4.145709137960235</v>
+        <v>-3.984691465303323</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-2.286594793045662</v>
       </c>
       <c r="E97">
-        <v>-37.84395628988345</v>
+        <v>-38.29630745453847</v>
       </c>
       <c r="F97">
-        <v>1.479297532304447</v>
+        <v>0.9974362140959742</v>
       </c>
       <c r="G97">
-        <v>-4.345778328211019</v>
+        <v>-4.361500232138704</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-2.21516463787562</v>
       </c>
       <c r="E98">
-        <v>-41.88082993568656</v>
+        <v>-40.1931434413632</v>
       </c>
       <c r="F98">
-        <v>0.6328079358338962</v>
+        <v>0.8179820134231005</v>
       </c>
       <c r="G98">
-        <v>-4.618251298207149</v>
+        <v>-4.88852341051297</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-2.166023570414445</v>
       </c>
       <c r="E99">
-        <v>-43.95424177859203</v>
+        <v>-42.4986699587907</v>
       </c>
       <c r="F99">
-        <v>0.20222753006313</v>
+        <v>0.8091963487490089</v>
       </c>
       <c r="G99">
-        <v>-4.821200139741931</v>
+        <v>-4.408115076813031</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-2.129564999062011</v>
       </c>
       <c r="E100">
-        <v>-44.76620497562433</v>
+        <v>-44.42889361145573</v>
       </c>
       <c r="F100">
-        <v>0.2358385374317199</v>
+        <v>0.4563366861785035</v>
       </c>
       <c r="G100">
-        <v>-5.090558491440862</v>
+        <v>-5.031741026547671</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-2.088939043367881</v>
       </c>
       <c r="E101">
-        <v>-48.21547709167653</v>
+        <v>-46.40302086103551</v>
       </c>
       <c r="F101">
-        <v>0.1390703141714872</v>
+        <v>0.02342194106664827</v>
       </c>
       <c r="G101">
-        <v>-5.369474779087859</v>
+        <v>-4.789132363929286</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-2.045522964032037</v>
       </c>
       <c r="E102">
-        <v>-47.61794938685929</v>
+        <v>-48.78992851607019</v>
       </c>
       <c r="F102">
-        <v>-0.4714621410812352</v>
+        <v>-0.1921432797964643</v>
       </c>
       <c r="G102">
-        <v>-5.741670360230742</v>
+        <v>-5.450345203542184</v>
       </c>
     </row>
   </sheetData>
